--- a/TestExcels/Hero.xlsx
+++ b/TestExcels/Hero.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="R6b0eb3fba2e940a5a02c34ad4367e9d1"/>
+    <x:sheet name="Sheet1" sheetId="1" state="visible" r:id="Re3489d9b22c44b469baea1b553bf1ce8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -122,7 +122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:D9"/>
+  <x:dimension ref="A1:H9"/>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str" s="1">
@@ -137,6 +137,18 @@
       <x:c r="D1" t="str" s="1">
         <x:v>D</x:v>
       </x:c>
+      <x:c r="E1" t="str" s="1">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="F1" t="str" s="1">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G1" t="str" s="1">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="H1" t="str" s="1">
+        <x:v>H</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str" s="2">
@@ -151,6 +163,18 @@
       <x:c r="D2" t="str" s="2">
         <x:v>hp</x:v>
       </x:c>
+      <x:c r="E2" t="str" s="2">
+        <x:v>level</x:v>
+      </x:c>
+      <x:c r="F2" t="str" s="2">
+        <x:v>enabled</x:v>
+      </x:c>
+      <x:c r="G2" t="str" s="2">
+        <x:v>rewards</x:v>
+      </x:c>
+      <x:c r="H2" t="str" s="2">
+        <x:v>tags</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str" s="2">
@@ -165,6 +189,18 @@
       <x:c r="D3" t="str" s="2">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="E3" t="str" s="2">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="F3" t="str" s="2">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="G3" t="str" s="2">
+        <x:v>int[]</x:v>
+      </x:c>
+      <x:c r="H3" t="str" s="2">
+        <x:v>string[]</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str" s="2">
@@ -179,6 +215,18 @@
       <x:c r="D4" t="str" s="2">
         <x:v>生命值</x:v>
       </x:c>
+      <x:c r="E4" t="str" s="2">
+        <x:v>等级</x:v>
+      </x:c>
+      <x:c r="F4" t="str" s="2">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="G4" t="str" s="2">
+        <x:v>奖励</x:v>
+      </x:c>
+      <x:c r="H4" t="str" s="2">
+        <x:v>标签</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str" s="2">
@@ -193,6 +241,18 @@
       <x:c r="D5" t="str" s="2">
         <x:v/>
       </x:c>
+      <x:c r="E5" t="str" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="F5" t="str" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="G5" t="str" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="H5" t="str" s="2">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str" s="2">
@@ -207,6 +267,18 @@
       <x:c r="D6" t="str" s="2">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="E6" t="str" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" t="str" s="2">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="G6" t="str" s="2">
+        <x:v>1|2|3</x:v>
+      </x:c>
+      <x:c r="H6" t="str" s="2">
+        <x:v>atk|def</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str" s="2">
@@ -221,6 +293,18 @@
       <x:c r="D7" t="str" s="2">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="E7" t="str" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" t="str" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" t="str" s="2">
+        <x:v>10|20</x:v>
+      </x:c>
+      <x:c r="H7" t="str" s="2">
+        <x:v>hp</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str" s="2">
@@ -235,6 +319,18 @@
       <x:c r="D8" t="str" s="2">
         <x:v>80</x:v>
       </x:c>
+      <x:c r="E8" t="str" s="2">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F8" t="str" s="2">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="G8" t="str" s="2">
+        <x:v/>
+      </x:c>
+      <x:c r="H8" t="str" s="2">
+        <x:v/>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str" s="2">
@@ -249,9 +345,21 @@
       <x:c r="D9" t="str" s="2">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="E9" t="str" s="2">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F9" t="str" s="2">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" t="str" s="2">
+        <x:v>5|6|7|8</x:v>
+      </x:c>
+      <x:c r="H9" t="str" s="2">
+        <x:v>skill|ult</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:D9"/>
+  <x:autoFilter ref="A1:H9"/>
   <x:drawing r:id="drawing1"/>
 </x:worksheet>
 </file>